--- a/tools/myCustomBlockly/iMi/CloudEspGps/ESP32CloudGps積木程式碼.xlsx
+++ b/tools/myCustomBlockly/iMi/CloudEspGps/ESP32CloudGps積木程式碼.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\maker\ArduinoMaster\tools\myCustomBlockly\iMi\CloudEspGps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A4139C9-E4BB-4B64-BB6A-BF9B06930D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45640D51-351E-4E87-8718-A8F2F93E1E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" tabRatio="737" firstSheet="2" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -879,7 +879,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>coordinates = {Lats[carX][carY], Longs[carX][carY]};</t>
+      <t>coordinates = {Lats[carX][carY], Longs[carX][carY]};\n}</t>
     </r>
     <r>
       <rPr>
@@ -890,6 +890,7 @@
       </rPr>
       <t>'</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -6477,7 +6478,7 @@
       </c>
       <c r="K1" s="6" t="str">
         <f>"var code ="&amp;_xlfn.CONCAT(J2)&amp;";"</f>
-        <v>var code = 'coordinates = {Lats[carX][carY], Longs[carX][carY]};'+'\n'+;</v>
+        <v>var code = 'coordinates = {Lats[carX][carY], Longs[carX][carY]};\n}'+'\n'+;</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="27.75" x14ac:dyDescent="0.25">
@@ -6498,7 +6499,7 @@
       </c>
       <c r="J2" s="18" t="str">
         <f>IF(ISBLANK(I2),"",I2&amp;"+'\n'+")</f>
-        <v xml:space="preserve"> 'coordinates = {Lats[carX][carY], Longs[carX][carY]};'+'\n'+</v>
+        <v xml:space="preserve"> 'coordinates = {Lats[carX][carY], Longs[carX][carY]};\n}'+'\n'+</v>
       </c>
       <c r="K2" s="34"/>
       <c r="L2" s="27" t="s">
